--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121119645</v>
+        <v>121122802</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>91102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509808</v>
+        <v>509936</v>
       </c>
       <c r="R2" t="n">
-        <v>6513858</v>
+        <v>6513900</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,28 +784,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121122802</v>
+        <v>121112512</v>
       </c>
       <c r="B3" t="n">
-        <v>91092</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,56 +815,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Unnagölen, Unnagölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509936</v>
+        <v>509651</v>
       </c>
       <c r="R3" t="n">
-        <v>6513900</v>
+        <v>6513903</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,29 +897,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121112512</v>
+        <v>121119982</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>4772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,41 +927,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Unnagölen, Unnagölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509651</v>
+        <v>509883</v>
       </c>
       <c r="R4" t="n">
-        <v>6513903</v>
+        <v>6513888</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,22 +1020,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121122850</v>
+        <v>121119645</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,50 +1044,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509668</v>
+        <v>509808</v>
       </c>
       <c r="R5" t="n">
-        <v>6513939</v>
+        <v>6513858</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,29 +1131,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121119982</v>
+        <v>121122850</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,42 +1165,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509883</v>
+        <v>509668</v>
       </c>
       <c r="R6" t="n">
-        <v>6513888</v>
+        <v>6513939</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,18 +1252,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121122802</v>
+        <v>121119982</v>
       </c>
       <c r="B2" t="n">
-        <v>91102</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,52 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509936</v>
+        <v>509883</v>
       </c>
       <c r="R2" t="n">
-        <v>6513900</v>
+        <v>6513888</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,19 +774,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -915,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121119982</v>
+        <v>121122802</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>91102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,42 +920,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509883</v>
+        <v>509936</v>
       </c>
       <c r="R4" t="n">
-        <v>6513888</v>
+        <v>6513900</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,28 +1013,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121119645</v>
+        <v>121122850</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,46 +1044,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509808</v>
+        <v>509668</v>
       </c>
       <c r="R5" t="n">
-        <v>6513858</v>
+        <v>6513939</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,28 +1135,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121122850</v>
+        <v>121119645</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,50 +1166,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509668</v>
+        <v>509808</v>
       </c>
       <c r="R6" t="n">
-        <v>6513939</v>
+        <v>6513858</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,19 +1253,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121119982</v>
+        <v>121122802</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>91114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509883</v>
+        <v>509936</v>
       </c>
       <c r="R2" t="n">
-        <v>6513888</v>
+        <v>6513900</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,18 +784,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +806,7 @@
         <v>121112512</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121122802</v>
+        <v>121119645</v>
       </c>
       <c r="B4" t="n">
-        <v>91102</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,56 +927,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509936</v>
+        <v>509808</v>
       </c>
       <c r="R4" t="n">
-        <v>6513900</v>
+        <v>6513858</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1014,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121119645</v>
+        <v>121119982</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,31 +1166,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>mina</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509808</v>
+        <v>509883</v>
       </c>
       <c r="R6" t="n">
-        <v>6513858</v>
+        <v>6513888</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121122802</v>
+        <v>121122850</v>
       </c>
       <c r="B2" t="n">
-        <v>91114</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -730,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509936</v>
+        <v>509668</v>
       </c>
       <c r="R2" t="n">
-        <v>6513900</v>
+        <v>6513939</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121119645</v>
+        <v>121122802</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>91115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,46 +921,56 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509808</v>
+        <v>509936</v>
       </c>
       <c r="R4" t="n">
-        <v>6513858</v>
+        <v>6513900</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,28 +1018,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121122850</v>
+        <v>121119645</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>92021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,50 +1049,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509668</v>
+        <v>509808</v>
       </c>
       <c r="R5" t="n">
-        <v>6513939</v>
+        <v>6513858</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,19 +1136,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121122850</v>
+        <v>121122802</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>91118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509668</v>
+        <v>509936</v>
       </c>
       <c r="R2" t="n">
-        <v>6513939</v>
+        <v>6513900</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112512</v>
+        <v>121119645</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +819,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Unnagölen, Unnagölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509651</v>
+        <v>509808</v>
       </c>
       <c r="R3" t="n">
-        <v>6513903</v>
+        <v>6513858</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +908,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121122802</v>
+        <v>121112512</v>
       </c>
       <c r="B4" t="n">
-        <v>91115</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,56 +932,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Unnagölen, Unnagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509936</v>
+        <v>509651</v>
       </c>
       <c r="R4" t="n">
-        <v>6513900</v>
+        <v>6513903</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,29 +1014,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121119645</v>
+        <v>121119982</v>
       </c>
       <c r="B5" t="n">
-        <v>92021</v>
+        <v>4775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,31 +1044,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>mina</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509808</v>
+        <v>509883</v>
       </c>
       <c r="R5" t="n">
-        <v>6513858</v>
+        <v>6513888</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121119982</v>
+        <v>121122850</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>5172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,42 +1165,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509883</v>
+        <v>509668</v>
       </c>
       <c r="R6" t="n">
-        <v>6513888</v>
+        <v>6513939</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,18 +1252,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121119645</v>
+        <v>121122850</v>
       </c>
       <c r="B3" t="n">
-        <v>92024</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,46 +815,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallskog runt Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509808</v>
+        <v>509668</v>
       </c>
       <c r="R3" t="n">
-        <v>6513858</v>
+        <v>6513939</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,28 +906,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Rosén, Emil Lindgren</t>
+          <t>Emil Lindgren, William Rosén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121112512</v>
+        <v>121119645</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,37 +941,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Unnagölen, Unnagölen, Ög</t>
+          <t>Tallskog runt Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509651</v>
+        <v>509808</v>
       </c>
       <c r="R4" t="n">
-        <v>6513903</v>
+        <v>6513858</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,12 +1030,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>William Rosén, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1149,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121122850</v>
+        <v>121112512</v>
       </c>
       <c r="B6" t="n">
-        <v>5172</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,50 +1171,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Unnagölen, Unnagölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509668</v>
+        <v>509651</v>
       </c>
       <c r="R6" t="n">
-        <v>6513939</v>
+        <v>6513903</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,19 +1253,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Lindgren, William Rosén</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,6 +1269,230 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121665328</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94770</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>510009</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6513895</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121665329</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91125</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>509977</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6513920</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -1274,7 +1274,7 @@
         <v>121665328</v>
       </c>
       <c r="B7" t="n">
-        <v>94770</v>
+        <v>94778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>121665329</v>
       </c>
       <c r="B8" t="n">
-        <v>91125</v>
+        <v>91133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121665329</v>
+        <v>121665328</v>
       </c>
       <c r="B7" t="n">
-        <v>91133</v>
+        <v>94778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509977</v>
+        <v>510009</v>
       </c>
       <c r="R7" t="n">
-        <v>6513920</v>
+        <v>6513895</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121665328</v>
+        <v>121665329</v>
       </c>
       <c r="B8" t="n">
-        <v>94778</v>
+        <v>91133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510009</v>
+        <v>509977</v>
       </c>
       <c r="R8" t="n">
-        <v>6513895</v>
+        <v>6513920</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>01:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>01:52</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49705-2024 artfynd.xlsx
+++ b/artfynd/A 49705-2024 artfynd.xlsx
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121665328</v>
+        <v>121665329</v>
       </c>
       <c r="B7" t="n">
-        <v>94778</v>
+        <v>91133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510009</v>
+        <v>509977</v>
       </c>
       <c r="R7" t="n">
-        <v>6513895</v>
+        <v>6513920</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>01:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>01:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121665329</v>
+        <v>121665328</v>
       </c>
       <c r="B8" t="n">
-        <v>91133</v>
+        <v>94778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509977</v>
+        <v>510009</v>
       </c>
       <c r="R8" t="n">
-        <v>6513920</v>
+        <v>6513895</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>01:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
